--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:42</t>
+    <t xml:space="preserve">2026-09-09 22:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:29</t>
+    <t xml:space="preserve">2026-09-12 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
@@ -39,13 +39,37 @@
     <t xml:space="preserve">La Serena</t>
   </si>
   <si>
+    <t xml:space="preserve">Vicuña</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combarbalá</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Punitaqui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Los Vilos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salamanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Hurtado</t>
+  </si>
+  <si>
     <t xml:space="preserve">Canela</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Vilos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Salamanca</t>
+    <t xml:space="preserve">Illapel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andacollo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monte Patria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paihuano</t>
   </si>
   <si>
     <t xml:space="preserve">La Higuera</t>
@@ -54,37 +78,13 @@
     <t xml:space="preserve">Ovalle</t>
   </si>
   <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Illapel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Hurtado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Punitaqui</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andacollo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monte Patria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combarbalá</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vicuña</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:45</t>
+    <t xml:space="preserve">2026-09-24 00:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -517,7 +517,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11022</v>
+        <v>4977</v>
       </c>
     </row>
     <row r="3">
@@ -534,7 +534,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7276</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="4">
@@ -545,13 +545,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4202</v>
+        <v>4106</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>961</v>
+        <v>833</v>
       </c>
     </row>
     <row r="5">
@@ -562,13 +562,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4203</v>
+        <v>4302</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>707</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6">
@@ -579,13 +579,13 @@
         <v>9</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4204</v>
+        <v>4304</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>669</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7">
@@ -596,13 +596,13 @@
         <v>10</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4104</v>
+        <v>4203</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>361</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8">
@@ -613,13 +613,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4301</v>
+        <v>4204</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>293</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -630,13 +630,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4105</v>
+        <v>4305</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>221</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10">
@@ -647,13 +647,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4201</v>
+        <v>4202</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>185</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11">
@@ -664,13 +664,13 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4305</v>
+        <v>4201</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>162</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12">
@@ -681,13 +681,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4304</v>
+        <v>4103</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>139</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13">
@@ -698,13 +698,13 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4103</v>
+        <v>4303</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>34</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14">
@@ -715,13 +715,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4303</v>
+        <v>4105</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-65</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -732,13 +732,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4302</v>
+        <v>4104</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-85</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
@@ -749,13 +749,13 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4106</v>
+        <v>4301</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-164</v>
+        <v>-204</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:23</t>
+    <t xml:space="preserve">2026-09-27 22:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:12</t>
+    <t xml:space="preserve">2026-10-01 20:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:53</t>
+    <t xml:space="preserve">2026-10-02 13:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:17</t>
+    <t xml:space="preserve">2026-10-04 08:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_coquimbo.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:07</t>
+    <t xml:space="preserve">2026-10-05 07:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
